--- a/data/Large-scale analysis.xlsx
+++ b/data/Large-scale analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\song\Desktop\work4图\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\song\Desktop\work4\data\Large-scale analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28511C1E-C2FA-4236-8C45-D4F69D7BC4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7D7F77-823A-4A75-A5D6-7E9A6B4BC303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,21 +25,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t>CVE</t>
+    <t>653(1,846)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Vulnerable API</t>
+    <t>#Vulnerable API</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Lib(Libv)</t>
+    <t>#CVE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>653(1,846)</t>
+    <t>#Lib(Libv)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#CWE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -383,33 +387,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.4140625" customWidth="1"/>
-    <col min="3" max="3" width="16.58203125" customWidth="1"/>
+    <col min="1" max="1" width="16.58203125" customWidth="1"/>
+    <col min="2" max="2" width="23.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3">
         <v>123271</v>
       </c>
-      <c r="B2" s="3">
+      <c r="C2" s="3">
         <v>1250</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
+      <c r="D2" s="1">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
